--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>SXTC</t>
   </si>
@@ -656,265 +656,278 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44104</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43921</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43555</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43373</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43190</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43008</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42825</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>900</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>1200</v>
       </c>
       <c r="M9" s="3">
         <v>1200</v>
       </c>
       <c r="N9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
       <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3">
         <v>2900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,8 +948,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -991,8 +1005,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1047,8 +1064,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1058,24 +1078,24 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>5600</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1091,8 +1111,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1103,8 +1123,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1159,8 +1182,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1178,120 +1204,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E17" s="3">
         <v>5200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3900</v>
       </c>
       <c r="G17" s="3">
         <v>3900</v>
       </c>
       <c r="H17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I17" s="3">
         <v>4300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1312,38 +1345,39 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1357,99 +1391,105 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>400</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>2900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1462,8 +1502,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1480,69 +1520,75 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1551,49 +1597,52 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
       </c>
       <c r="Q24" s="3">
+        <v>300</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1648,120 +1697,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1816,8 +1874,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1872,8 +1933,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1928,8 +1992,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1984,38 +2051,41 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2029,75 +2099,81 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2152,125 +2228,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44104</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43921</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43555</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43373</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43190</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43008</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42825</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2291,8 +2376,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2313,49 +2399,50 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E41" s="3">
         <v>17400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15500</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>13300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
@@ -2369,8 +2456,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2425,8 +2515,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2434,41 +2527,41 @@
         <v>1300</v>
       </c>
       <c r="E43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F43" s="3">
         <v>8100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5900</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2481,8 +2574,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2490,16 +2586,16 @@
         <v>500</v>
       </c>
       <c r="E44" s="3">
+        <v>500</v>
+      </c>
+      <c r="F44" s="3">
         <v>600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>800</v>
-      </c>
-      <c r="H44" s="3">
-        <v>900</v>
       </c>
       <c r="I44" s="3">
         <v>900</v>
@@ -2508,23 +2604,23 @@
         <v>900</v>
       </c>
       <c r="K44" s="3">
+        <v>900</v>
+      </c>
+      <c r="L44" s="3">
         <v>800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1500</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2537,8 +2633,11 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2546,41 +2645,41 @@
         <v>300</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,50 +2692,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E46" s="3">
         <v>19500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,38 +2751,41 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>3500</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,8 +2798,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2705,28 +2810,31 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1900</v>
       </c>
       <c r="J48" s="3">
         <v>1900</v>
@@ -2735,20 +2843,20 @@
         <v>1900</v>
       </c>
       <c r="L48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2761,8 +2869,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2785,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -2800,10 +2911,10 @@
         <v>100</v>
       </c>
       <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2817,8 +2928,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2873,8 +2987,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2929,35 +3046,38 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>8700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>9500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9500</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -2967,8 +3087,8 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -2985,8 +3105,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3041,50 +3164,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E54" s="3">
         <v>29600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>33500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>24000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,8 +3223,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3119,8 +3248,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3141,19 +3271,20 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1500</v>
       </c>
       <c r="G57" s="3">
         <v>1500</v>
@@ -3162,29 +3293,29 @@
         <v>1500</v>
       </c>
       <c r="I57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3197,23 +3328,26 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -3221,26 +3355,26 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>6700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3253,50 +3387,53 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E59" s="3">
         <v>9800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3309,50 +3446,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E60" s="3">
         <v>14500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3365,8 +3505,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3374,7 +3517,7 @@
         <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -3392,11 +3535,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3421,16 +3564,19 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
         <v>200</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="E62" s="3">
+        <v>200</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -3447,8 +3593,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3465,20 +3611,23 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3533,8 +3682,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3589,8 +3741,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3645,50 +3800,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E66" s="3">
         <v>14900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>17100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3701,8 +3859,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3723,8 +3884,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3779,8 +3941,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3835,8 +4000,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3891,8 +4059,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3947,50 +4118,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-21600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-17200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-15700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-7200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,8 +4177,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4059,8 +4236,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4115,8 +4295,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4171,50 +4354,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E76" s="3">
         <v>14700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4227,8 +4413,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4283,125 +4472,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44104</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43921</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43555</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43373</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43190</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43008</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42825</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4422,8 +4620,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4437,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -4449,22 +4648,22 @@
         <v>200</v>
       </c>
       <c r="K83" s="3">
+        <v>200</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>100</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>100</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4478,8 +4677,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4534,8 +4736,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4590,8 +4795,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4646,8 +4854,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4702,8 +4913,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4758,50 +4972,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4814,8 +5031,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4836,17 +5056,18 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -4857,28 +5078,28 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4892,8 +5113,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4948,8 +5172,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5004,50 +5231,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>9300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2700</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-5500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
         <v>-1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5290,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5082,8 +5315,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5138,8 +5372,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5194,8 +5431,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5250,8 +5490,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5306,49 +5549,52 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E100" s="3">
         <v>14000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>-300</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>-300</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -5362,49 +5608,52 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="F101" s="3">
-        <v>200</v>
       </c>
       <c r="G101" s="3">
         <v>200</v>
       </c>
       <c r="H101" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I101" s="3">
         <v>400</v>
       </c>
       <c r="J101" s="3">
+        <v>400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -5418,49 +5667,52 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E102" s="3">
         <v>14400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1000</v>
       </c>
       <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>-1000</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5472,6 +5724,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>SXTC</t>
   </si>
@@ -656,160 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43373</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43190</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43008</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42825</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42735</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -817,117 +824,123 @@
         <v>700</v>
       </c>
       <c r="E9" s="3">
+        <v>700</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1400</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1200</v>
       </c>
       <c r="N9" s="3">
         <v>1200</v>
       </c>
       <c r="O9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>2900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -949,8 +962,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1008,8 +1022,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1067,8 +1084,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1081,24 +1101,24 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>5600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,8 +1134,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1126,8 +1146,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1185,8 +1208,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1205,126 +1231,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E17" s="3">
         <v>10300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3900</v>
       </c>
       <c r="H17" s="3">
         <v>3900</v>
       </c>
       <c r="I17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J17" s="3">
         <v>4300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1346,8 +1379,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1355,32 +1389,32 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1394,105 +1428,111 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1505,8 +1545,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1523,75 +1563,81 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1600,49 +1646,52 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
-      </c>
-      <c r="P24" s="3">
-        <v>300</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
+        <v>300</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1700,126 +1749,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1877,8 +1935,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1936,8 +1997,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1995,8 +2059,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2054,8 +2121,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2063,32 +2133,32 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2102,78 +2172,84 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2231,131 +2307,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43373</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43190</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43008</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42825</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42735</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2377,8 +2462,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2400,52 +2486,53 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E41" s="3">
         <v>11500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15500</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>13300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>600</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
+      <c r="Q41" s="3">
+        <v>0</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
@@ -2459,8 +2546,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2518,8 +2608,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2530,41 +2623,41 @@
         <v>1300</v>
       </c>
       <c r="F43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G43" s="3">
         <v>8100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5900</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,28 +2670,31 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E44" s="3">
         <v>500</v>
       </c>
       <c r="F44" s="3">
+        <v>500</v>
+      </c>
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>800</v>
-      </c>
-      <c r="I44" s="3">
-        <v>900</v>
       </c>
       <c r="J44" s="3">
         <v>900</v>
@@ -2607,23 +2703,23 @@
         <v>900</v>
       </c>
       <c r="L44" s="3">
+        <v>900</v>
+      </c>
+      <c r="M44" s="3">
         <v>800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1500</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2636,53 +2732,56 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
       </c>
       <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,53 +2794,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E46" s="3">
         <v>13500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2754,8 +2856,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2780,15 +2885,15 @@
       <c r="J47" s="3">
         <v>0</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>3500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2801,8 +2906,8 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -2813,31 +2918,34 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1900</v>
       </c>
       <c r="K48" s="3">
         <v>1900</v>
@@ -2846,20 +2954,20 @@
         <v>1900</v>
       </c>
       <c r="M48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2872,8 +2980,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2899,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>100</v>
@@ -2914,10 +3025,10 @@
         <v>100</v>
       </c>
       <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -2931,8 +3042,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2990,8 +3104,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3049,38 +3166,41 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="E52" s="3">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3">
         <v>8700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9500</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3090,8 +3210,8 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3108,8 +3228,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3167,53 +3290,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E54" s="3">
         <v>14600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>33500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>34500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3352,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3249,8 +3378,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3272,8 +3402,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3281,13 +3412,13 @@
         <v>1300</v>
       </c>
       <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1500</v>
       </c>
       <c r="H57" s="3">
         <v>1500</v>
@@ -3296,29 +3427,29 @@
         <v>1500</v>
       </c>
       <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,26 +3462,29 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E58" s="3">
         <v>2800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3358,26 +3492,26 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>6700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3390,53 +3524,56 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E59" s="3">
         <v>5100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3449,53 +3586,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E60" s="3">
         <v>9200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>17100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5100</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3508,8 +3648,11 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3520,7 +3663,7 @@
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -3538,11 +3681,11 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3567,8 +3710,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3578,8 +3724,8 @@
       <c r="E62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
+      <c r="F62" s="3">
+        <v>200</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -3596,8 +3742,8 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -3614,20 +3760,23 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3685,8 +3834,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3744,8 +3896,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3803,53 +3958,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E66" s="3">
         <v>9500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>17100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +4020,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3885,8 +4046,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3944,8 +4106,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4003,8 +4168,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4062,8 +4230,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4121,53 +4292,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-31300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-21600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-17200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-15700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-13000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-10000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-7200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4354,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4239,8 +4416,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4298,8 +4478,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4357,53 +4540,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>14900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4416,8 +4602,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4475,131 +4664,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43373</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43190</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43008</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42825</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42735</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4621,8 +4819,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4639,7 +4838,7 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -4651,22 +4850,22 @@
         <v>200</v>
       </c>
       <c r="L83" s="3">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>100</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4680,8 +4879,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4739,8 +4941,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4798,8 +5003,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4857,8 +5065,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4916,8 +5127,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4975,53 +5189,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5034,8 +5251,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5057,8 +5277,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5066,11 +5287,11 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -5081,28 +5302,28 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -5116,8 +5337,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5175,8 +5399,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5234,8 +5461,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5243,44 +5473,44 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>9300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2700</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-5500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5293,8 +5523,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5316,8 +5549,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5375,8 +5609,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5434,8 +5671,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5493,8 +5733,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5552,52 +5795,55 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>14000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
-        <v>-300</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>-300</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5611,52 +5857,55 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1000</v>
-      </c>
-      <c r="G101" s="3">
-        <v>200</v>
       </c>
       <c r="H101" s="3">
         <v>200</v>
       </c>
       <c r="I101" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="J101" s="3">
         <v>400</v>
       </c>
       <c r="K101" s="3">
+        <v>400</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -5670,52 +5919,55 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-12600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1000</v>
       </c>
       <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>-1000</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>500</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
@@ -5727,6 +5979,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>SXTC</t>
   </si>
@@ -663,13 +663,10 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -700,22 +697,22 @@
         <v>45382</v>
       </c>
       <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J7" s="2">
         <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44286</v>
       </c>
       <c r="K7" s="2">
         <v>44104</v>
@@ -759,25 +756,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E8" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="F8" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G8" s="3">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="H8" s="3">
-        <v>1600</v>
+        <v>400</v>
       </c>
       <c r="I8" s="3">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="J8" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="K8" s="3">
         <v>3900</v>
@@ -821,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G9" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>200</v>
+      </c>
+      <c r="J9" s="3">
         <v>600</v>
-      </c>
-      <c r="I9" s="3">
-        <v>700</v>
-      </c>
-      <c r="J9" s="3">
-        <v>900</v>
       </c>
       <c r="K9" s="3">
         <v>1000</v>
@@ -883,22 +880,22 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
       </c>
       <c r="H10" s="3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="I10" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J10" s="3">
         <v>0</v>
@@ -1092,11 +1089,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>200</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1105,13 +1102,13 @@
         <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>200</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -1155,25 +1152,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1238,25 +1235,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>-5800</v>
+        <v>-3100</v>
       </c>
       <c r="E17" s="3">
-        <v>10300</v>
+        <v>-3100</v>
       </c>
       <c r="F17" s="3">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="G17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H17" s="3">
         <v>2400</v>
       </c>
-      <c r="H17" s="3">
-        <v>3900</v>
-      </c>
       <c r="I17" s="3">
-        <v>3900</v>
+        <v>2400</v>
       </c>
       <c r="J17" s="3">
-        <v>4300</v>
+        <v>1200</v>
       </c>
       <c r="K17" s="3">
         <v>2700</v>
@@ -1300,25 +1297,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6800</v>
+        <v>3600</v>
       </c>
       <c r="E18" s="3">
-        <v>-9400</v>
+        <v>3600</v>
       </c>
       <c r="F18" s="3">
-        <v>-4400</v>
+        <v>-4700</v>
       </c>
       <c r="G18" s="3">
-        <v>-1200</v>
+        <v>-4700</v>
       </c>
       <c r="H18" s="3">
-        <v>-2300</v>
+        <v>-2100</v>
       </c>
       <c r="I18" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="J18" s="3">
-        <v>-3400</v>
+        <v>-600</v>
       </c>
       <c r="K18" s="3">
         <v>1200</v>
@@ -1392,19 +1389,19 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>900</v>
@@ -1448,25 +1445,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>6900</v>
+        <v>3700</v>
       </c>
       <c r="E21" s="3">
-        <v>-9300</v>
+        <v>3700</v>
       </c>
       <c r="F21" s="3">
-        <v>-4200</v>
+        <v>-4600</v>
       </c>
       <c r="G21" s="3">
-        <v>-1000</v>
+        <v>-4600</v>
       </c>
       <c r="H21" s="3">
-        <v>-2500</v>
+        <v>-1900</v>
       </c>
       <c r="I21" s="3">
-        <v>-2600</v>
+        <v>-1900</v>
       </c>
       <c r="J21" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="K21" s="3">
         <v>2300</v>
@@ -1510,25 +1507,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
-        <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>100</v>
-      </c>
       <c r="G22" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J22" s="3">
-        <v>2900</v>
+        <v>200</v>
       </c>
       <c r="K22" s="3">
         <v>500</v>
@@ -1572,25 +1569,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E23" s="3">
-        <v>-9700</v>
+        <v>3300</v>
       </c>
       <c r="F23" s="3">
-        <v>-4400</v>
+        <v>-4800</v>
       </c>
       <c r="G23" s="3">
-        <v>-1500</v>
+        <v>-4800</v>
       </c>
       <c r="H23" s="3">
-        <v>-2600</v>
+        <v>-2200</v>
       </c>
       <c r="I23" s="3">
-        <v>-2800</v>
+        <v>-2200</v>
       </c>
       <c r="J23" s="3">
-        <v>-4600</v>
+        <v>-700</v>
       </c>
       <c r="K23" s="3">
         <v>1600</v>
@@ -1639,20 +1636,20 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-400</v>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>200</v>
@@ -1758,25 +1755,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E26" s="3">
-        <v>-9700</v>
+        <v>3300</v>
       </c>
       <c r="F26" s="3">
-        <v>-4400</v>
+        <v>-4800</v>
       </c>
       <c r="G26" s="3">
-        <v>-1500</v>
+        <v>-4800</v>
       </c>
       <c r="H26" s="3">
-        <v>-2600</v>
+        <v>-2200</v>
       </c>
       <c r="I26" s="3">
-        <v>-3100</v>
+        <v>-2200</v>
       </c>
       <c r="J26" s="3">
-        <v>-4100</v>
+        <v>-700</v>
       </c>
       <c r="K26" s="3">
         <v>1400</v>
@@ -1820,25 +1817,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E27" s="3">
-        <v>-9700</v>
+        <v>3300</v>
       </c>
       <c r="F27" s="3">
-        <v>-4400</v>
+        <v>-4800</v>
       </c>
       <c r="G27" s="3">
-        <v>-1500</v>
+        <v>-4800</v>
       </c>
       <c r="H27" s="3">
-        <v>-2600</v>
+        <v>-2200</v>
       </c>
       <c r="I27" s="3">
-        <v>-3100</v>
+        <v>-2200</v>
       </c>
       <c r="J27" s="3">
-        <v>-4100</v>
+        <v>-700</v>
       </c>
       <c r="K27" s="3">
         <v>1400</v>
@@ -2136,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>-900</v>
@@ -2192,25 +2189,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E33" s="3">
-        <v>-9700</v>
+        <v>3300</v>
       </c>
       <c r="F33" s="3">
-        <v>-4400</v>
+        <v>-4800</v>
       </c>
       <c r="G33" s="3">
-        <v>-1500</v>
+        <v>-4800</v>
       </c>
       <c r="H33" s="3">
-        <v>-2600</v>
+        <v>-2200</v>
       </c>
       <c r="I33" s="3">
-        <v>-3100</v>
+        <v>-2200</v>
       </c>
       <c r="J33" s="3">
-        <v>-4100</v>
+        <v>-700</v>
       </c>
       <c r="K33" s="3">
         <v>1400</v>
@@ -2316,25 +2313,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E35" s="3">
-        <v>-9700</v>
+        <v>3300</v>
       </c>
       <c r="F35" s="3">
-        <v>-4400</v>
+        <v>-4800</v>
       </c>
       <c r="G35" s="3">
-        <v>-1500</v>
+        <v>-4800</v>
       </c>
       <c r="H35" s="3">
-        <v>-2600</v>
+        <v>-2200</v>
       </c>
       <c r="I35" s="3">
-        <v>-3100</v>
+        <v>-2200</v>
       </c>
       <c r="J35" s="3">
-        <v>-4100</v>
+        <v>-700</v>
       </c>
       <c r="K35" s="3">
         <v>1400</v>
@@ -2386,22 +2383,22 @@
         <v>45382</v>
       </c>
       <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J38" s="2">
         <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44286</v>
       </c>
       <c r="K38" s="2">
         <v>44104</v>
@@ -2496,22 +2493,22 @@
         <v>12100</v>
       </c>
       <c r="E41" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F41" s="3">
         <v>11500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H41" s="3">
         <v>17400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>17400</v>
+      </c>
+      <c r="J41" s="3">
         <v>3000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>15500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>13300</v>
       </c>
       <c r="K41" s="3">
         <v>10400</v>
@@ -2626,16 +2623,16 @@
         <v>1300</v>
       </c>
       <c r="G43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J43" s="3">
         <v>8100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>6700</v>
       </c>
       <c r="K43" s="3">
         <v>8400</v>
@@ -2682,22 +2679,22 @@
         <v>800</v>
       </c>
       <c r="E44" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="F44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>600</v>
       </c>
       <c r="H44" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="I44" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J44" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="K44" s="3">
         <v>900</v>
@@ -2740,26 +2737,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
+        <v>200</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2400</v>
       </c>
       <c r="K45" s="3">
         <v>2500</v>
@@ -2806,22 +2803,22 @@
         <v>14200</v>
       </c>
       <c r="E46" s="3">
+        <v>14200</v>
+      </c>
+      <c r="F46" s="3">
         <v>13500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>13500</v>
+      </c>
+      <c r="H46" s="3">
         <v>19500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>19500</v>
+      </c>
+      <c r="J46" s="3">
         <v>12400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>22500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J46" s="3">
-        <v>23200</v>
       </c>
       <c r="K46" s="3">
         <v>22100</v>
@@ -2864,26 +2861,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2930,22 +2927,22 @@
         <v>600</v>
       </c>
       <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J48" s="3">
         <v>1400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1800</v>
       </c>
       <c r="K48" s="3">
         <v>1900</v>
@@ -3178,22 +3175,22 @@
         <v>8300</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>8700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J52" s="3">
         <v>8400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>9500</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3302,22 +3299,22 @@
         <v>23100</v>
       </c>
       <c r="E54" s="3">
+        <v>23100</v>
+      </c>
+      <c r="F54" s="3">
         <v>14600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H54" s="3">
         <v>29600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>29600</v>
+      </c>
+      <c r="J54" s="3">
         <v>22200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>33500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>22700</v>
-      </c>
-      <c r="J54" s="3">
-        <v>34500</v>
       </c>
       <c r="K54" s="3">
         <v>24000</v>
@@ -3415,19 +3412,19 @@
         <v>1300</v>
       </c>
       <c r="F57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J57" s="3">
         <v>1600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1500</v>
       </c>
       <c r="K57" s="3">
         <v>1400</v>
@@ -3471,25 +3468,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2300</v>
+        <v>3400</v>
       </c>
       <c r="E58" s="3">
-        <v>2800</v>
+        <v>3400</v>
       </c>
       <c r="F58" s="3">
         <v>3300</v>
       </c>
       <c r="G58" s="3">
-        <v>1200</v>
+        <v>3300</v>
       </c>
       <c r="H58" s="3">
-        <v>2000</v>
+        <v>8600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3533,25 +3530,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5300</v>
+        <v>2600</v>
       </c>
       <c r="E59" s="3">
-        <v>5100</v>
+        <v>2600</v>
       </c>
       <c r="F59" s="3">
-        <v>9800</v>
+        <v>2500</v>
       </c>
       <c r="G59" s="3">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="H59" s="3">
-        <v>13600</v>
+        <v>2800</v>
       </c>
       <c r="I59" s="3">
-        <v>7400</v>
+        <v>2800</v>
       </c>
       <c r="J59" s="3">
-        <v>17100</v>
+        <v>2600</v>
       </c>
       <c r="K59" s="3">
         <v>4100</v>
@@ -3598,22 +3595,22 @@
         <v>8900</v>
       </c>
       <c r="E60" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H60" s="3">
         <v>14500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J60" s="3">
         <v>7300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J60" s="3">
-        <v>18600</v>
       </c>
       <c r="K60" s="3">
         <v>5500</v>
@@ -3657,22 +3654,22 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3718,14 +3715,14 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>200</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>3</v>
@@ -3970,22 +3967,22 @@
         <v>9200</v>
       </c>
       <c r="E66" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F66" s="3">
         <v>9500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>9500</v>
+      </c>
+      <c r="H66" s="3">
         <v>14900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>14900</v>
+      </c>
+      <c r="J66" s="3">
         <v>7300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>17100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>8900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>18600</v>
       </c>
       <c r="K66" s="3">
         <v>5500</v>
@@ -4304,22 +4301,22 @@
         <v>-24700</v>
       </c>
       <c r="E72" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-31300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="H72" s="3">
         <v>-21600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="J72" s="3">
         <v>-17200</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-13000</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-10000</v>
       </c>
       <c r="K72" s="3">
         <v>-5800</v>
@@ -4552,22 +4549,22 @@
         <v>13900</v>
       </c>
       <c r="E76" s="3">
+        <v>13900</v>
+      </c>
+      <c r="F76" s="3">
         <v>5100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H76" s="3">
         <v>14700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>14700</v>
+      </c>
+      <c r="J76" s="3">
         <v>14900</v>
-      </c>
-      <c r="H76" s="3">
-        <v>16400</v>
-      </c>
-      <c r="I76" s="3">
-        <v>13800</v>
-      </c>
-      <c r="J76" s="3">
-        <v>16000</v>
       </c>
       <c r="K76" s="3">
         <v>18500</v>
@@ -4681,22 +4678,22 @@
         <v>45382</v>
       </c>
       <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="J80" s="2">
         <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44469</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44286</v>
       </c>
       <c r="K80" s="2">
         <v>44104</v>
@@ -4740,25 +4737,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6600</v>
+        <v>3300</v>
       </c>
       <c r="E81" s="3">
-        <v>-9700</v>
+        <v>3300</v>
       </c>
       <c r="F81" s="3">
-        <v>-4400</v>
+        <v>-4800</v>
       </c>
       <c r="G81" s="3">
-        <v>-1500</v>
+        <v>-4800</v>
       </c>
       <c r="H81" s="3">
-        <v>-2600</v>
+        <v>-2200</v>
       </c>
       <c r="I81" s="3">
-        <v>-3100</v>
+        <v>-2200</v>
       </c>
       <c r="J81" s="3">
-        <v>-4100</v>
+        <v>-700</v>
       </c>
       <c r="K81" s="3">
         <v>1400</v>
@@ -4841,10 +4838,10 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5198,25 +5195,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1300</v>
+        <v>-700</v>
       </c>
       <c r="E89" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="F89" s="3">
-        <v>500</v>
+        <v>-300</v>
       </c>
       <c r="G89" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="H89" s="3">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="I89" s="3">
+        <v>200</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1000</v>
       </c>
       <c r="K89" s="3">
         <v>-300</v>
@@ -5289,11 +5286,11 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -5476,19 +5473,19 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
-        <v>9300</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-9300</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
-        <v>-8500</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>2700</v>
@@ -5555,26 +5552,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5804,25 +5801,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="E100" s="3">
-        <v>-4500</v>
+        <v>900</v>
       </c>
       <c r="F100" s="3">
-        <v>14000</v>
+        <v>-2200</v>
       </c>
       <c r="G100" s="3">
-        <v>-11100</v>
+        <v>-2200</v>
       </c>
       <c r="H100" s="3">
-        <v>5500</v>
+        <v>7000</v>
       </c>
       <c r="I100" s="3">
-        <v>-3900</v>
+        <v>7000</v>
       </c>
       <c r="J100" s="3">
-        <v>12100</v>
+        <v>-5500</v>
       </c>
       <c r="K100" s="3">
         <v>300</v>
@@ -5866,25 +5863,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H101" s="3">
-        <v>200</v>
-      </c>
       <c r="I101" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J101" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="K101" s="3">
         <v>400</v>
@@ -5928,25 +5925,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="E102" s="3">
-        <v>-5900</v>
+        <v>300</v>
       </c>
       <c r="F102" s="3">
-        <v>14400</v>
+        <v>-3000</v>
       </c>
       <c r="G102" s="3">
-        <v>-12600</v>
+        <v>-3000</v>
       </c>
       <c r="H102" s="3">
-        <v>15500</v>
+        <v>7200</v>
       </c>
       <c r="I102" s="3">
-        <v>-13300</v>
+        <v>7200</v>
       </c>
       <c r="J102" s="3">
-        <v>3000</v>
+        <v>-6300</v>
       </c>
       <c r="K102" s="3">
         <v>3100</v>

--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>SXTC</t>
   </si>
@@ -656,110 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43008</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42825</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42735</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E8" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F8" s="3">
         <v>500</v>
@@ -768,114 +776,126 @@
         <v>500</v>
       </c>
       <c r="H8" s="3">
+        <v>500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>500</v>
+      </c>
+      <c r="J8" s="3">
         <v>400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>5600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -892,52 +912,58 @@
         <v>100</v>
       </c>
       <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2600</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S10" s="3">
-        <v>700</v>
       </c>
       <c r="T10" s="3">
         <v>1700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U10" s="3">
+        <v>700</v>
+      </c>
+      <c r="V10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +986,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1050,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,44 +1118,50 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>5600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1134,11 +1174,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1146,16 +1186,22 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1173,10 +1219,10 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1208,8 +1254,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1281,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>700</v>
+      </c>
+      <c r="F17" s="3">
         <v>-3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>-3100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-4700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-6800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>300</v>
       </c>
       <c r="Q18" s="3">
         <v>1300</v>
       </c>
       <c r="R18" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="S18" s="3">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="T18" s="3">
         <v>1100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U18" s="3">
+        <v>600</v>
+      </c>
+      <c r="V18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,8 +1443,10 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1395,29 +1463,29 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1428,114 +1496,126 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
         <v>3700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-4600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-7800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>-100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>-100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,11 +1625,11 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1563,70 +1643,82 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-4800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-4800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-8000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
-      </c>
-      <c r="O23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>300</v>
       </c>
       <c r="Q23" s="3">
         <v>1300</v>
       </c>
       <c r="R23" s="3">
+        <v>300</v>
+      </c>
+      <c r="S23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T23" s="3">
         <v>1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1651,44 +1743,50 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>-100</v>
       </c>
       <c r="O24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
-      </c>
-      <c r="S24" s="3">
-        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1847,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-4800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-4800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P26" s="3">
-        <v>200</v>
       </c>
       <c r="Q26" s="3">
         <v>1000</v>
       </c>
       <c r="R26" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="S26" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U26" s="3">
+        <v>400</v>
+      </c>
+      <c r="V26" s="3">
+        <v>800</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F27" s="3">
         <v>3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-4800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-4800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P27" s="3">
-        <v>200</v>
       </c>
       <c r="Q27" s="3">
         <v>1000</v>
       </c>
       <c r="R27" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="S27" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U27" s="3">
+        <v>400</v>
+      </c>
+      <c r="V27" s="3">
+        <v>800</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +2051,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2119,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2187,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,8 +2255,14 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2139,29 +2279,29 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2172,81 +2312,93 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-4800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-4800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P33" s="3">
-        <v>200</v>
       </c>
       <c r="Q33" s="3">
         <v>1000</v>
       </c>
       <c r="R33" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="S33" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U33" s="3">
+        <v>400</v>
+      </c>
+      <c r="V33" s="3">
+        <v>800</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2459,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-4800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-4800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P35" s="3">
-        <v>200</v>
       </c>
       <c r="Q35" s="3">
         <v>1000</v>
       </c>
       <c r="R35" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="S35" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U35" s="3">
+        <v>400</v>
+      </c>
+      <c r="V35" s="3">
+        <v>800</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43008</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42825</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42735</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2630,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,58 +2656,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F41" s="3">
         <v>12100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>600</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2546,8 +2720,14 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,16 +2788,22 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="E43" s="3">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="F43" s="3">
         <v>1300</v>
@@ -2626,41 +2812,41 @@
         <v>1300</v>
       </c>
       <c r="H43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J43" s="3">
         <v>1600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>8100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>8400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>9700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>6100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>4300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>4000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5900</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,22 +2856,28 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>800</v>
-      </c>
-      <c r="F44" s="3">
-        <v>600</v>
-      </c>
-      <c r="G44" s="3">
-        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>600</v>
@@ -2694,35 +2886,35 @@
         <v>600</v>
       </c>
       <c r="J44" s="3">
+        <v>600</v>
+      </c>
+      <c r="K44" s="3">
+        <v>600</v>
+      </c>
+      <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1500</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2732,59 +2924,65 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,59 +2992,65 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F46" s="3">
         <v>14200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>14200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>13500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>19500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>22100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>15600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>6500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>7500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +3060,14 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2882,21 +3092,21 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>3500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,11 +3116,11 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -2918,59 +3128,65 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1900</v>
       </c>
       <c r="M48" s="3">
         <v>1900</v>
       </c>
       <c r="N48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,8 +3196,14 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3010,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>100</v>
@@ -3025,13 +3247,13 @@
         <v>100</v>
       </c>
       <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="R49" s="3">
+        <v>100</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3042,8 +3264,14 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3332,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,55 +3400,61 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F52" s="3">
         <v>8300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>8700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>8400</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3228,8 +3468,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,59 +3536,65 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F54" s="3">
         <v>23100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>23100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>14600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>29600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>29600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>22200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>24000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>21700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>23000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>7700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>8100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3604,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3634,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,16 +3660,18 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="E57" s="3">
-        <v>1300</v>
+        <v>1700</v>
       </c>
       <c r="F57" s="3">
         <v>1300</v>
@@ -3418,41 +3680,41 @@
         <v>1300</v>
       </c>
       <c r="H57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="3">
         <v>1400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1600</v>
       </c>
       <c r="K57" s="3">
         <v>1400</v>
       </c>
       <c r="L57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N57" s="3">
         <v>1900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1700</v>
       </c>
       <c r="O57" s="3">
         <v>2000</v>
       </c>
       <c r="P57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>2900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,59 +3724,65 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F58" s="3">
         <v>3400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>8600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>8600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>6700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,59 +3792,65 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>4400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,59 +3860,65 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F60" s="3">
         <v>8900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>12300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>6300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5100</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3928,14 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3666,29 +3952,29 @@
         <v>300</v>
       </c>
       <c r="H61" s="3">
+        <v>300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>300</v>
+      </c>
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3710,8 +3996,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3742,11 +4034,11 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -3760,20 +4052,26 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +4132,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4200,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,59 +4268,65 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F66" s="3">
         <v>9200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>11600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>5100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4336,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4366,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4430,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4498,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4566,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,59 +4634,65 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-24700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-24700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-31300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-31300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-21600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-21600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-17200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-5800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-7200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4702,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4770,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4838,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,59 +4906,65 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F76" s="3">
         <v>13900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>13900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>14700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>14700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4974,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +5042,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43008</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42825</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42735</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-4800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-4800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P81" s="3">
-        <v>200</v>
       </c>
       <c r="Q81" s="3">
         <v>1000</v>
       </c>
       <c r="R81" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="S81" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U81" s="3">
+        <v>400</v>
+      </c>
+      <c r="V81" s="3">
+        <v>800</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,16 +5213,18 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>100</v>
@@ -4844,32 +5242,32 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4879,8 +5277,14 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5345,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5413,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5481,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5549,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,8 +5617,14 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5201,47 +5635,47 @@
         <v>-700</v>
       </c>
       <c r="F89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5251,8 +5685,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,58 +5715,60 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5337,8 +5779,14 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5847,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5915,14 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5488,32 +5948,32 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>2700</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-5500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5523,8 +5983,14 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +6013,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5573,11 +6041,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5609,8 +6077,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +6145,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +6213,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,59 +6281,65 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>7000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>7000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-5500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-3900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5857,58 +6349,64 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
-      </c>
-      <c r="H101" s="3">
-        <v>100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
       </c>
       <c r="J101" s="3">
         <v>100</v>
       </c>
       <c r="K101" s="3">
+        <v>100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>100</v>
+      </c>
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -5919,58 +6417,64 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>7200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>7200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -5979,6 +6483,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>SXTC</t>
   </si>
@@ -656,124 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43008</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42825</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42735</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>500</v>
       </c>
       <c r="H8" s="3">
         <v>500</v>
@@ -782,52 +789,58 @@
         <v>500</v>
       </c>
       <c r="J8" s="3">
+        <v>500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>500</v>
+      </c>
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>3100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -838,64 +851,70 @@
         <v>300</v>
       </c>
       <c r="F9" s="3">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>300</v>
+      </c>
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -918,52 +937,58 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>2900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2600</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="U10" s="3">
-        <v>700</v>
       </c>
       <c r="V10" s="3">
         <v>1700</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="W10" s="3">
+        <v>700</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1013,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1083,14 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1157,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1135,39 +1174,39 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>5600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,11 +1219,11 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1192,8 +1231,14 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1204,10 +1249,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1225,10 +1270,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1260,8 +1305,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1334,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>-3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>-3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-6800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R18" s="3">
-        <v>300</v>
       </c>
       <c r="S18" s="3">
         <v>1300</v>
       </c>
       <c r="T18" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="U18" s="3">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="V18" s="3">
         <v>1100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W18" s="3">
+        <v>600</v>
+      </c>
+      <c r="X18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1510,10 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1469,29 +1536,29 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1502,87 +1569,99 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>3700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-4600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-7800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1593,35 +1672,35 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>-100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>-100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1631,11 +1710,11 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1649,76 +1728,88 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-4800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-4800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>500</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>300</v>
       </c>
       <c r="S23" s="3">
         <v>1300</v>
       </c>
       <c r="T23" s="3">
+        <v>300</v>
+      </c>
+      <c r="U23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V23" s="3">
         <v>1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1749,44 +1840,50 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
         <v>200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>-100</v>
       </c>
       <c r="Q24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
       </c>
       <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>100</v>
+      </c>
+      <c r="X24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1950,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-4800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R26" s="3">
-        <v>200</v>
       </c>
       <c r="S26" s="3">
         <v>1000</v>
       </c>
       <c r="T26" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="U26" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W26" s="3">
+        <v>400</v>
+      </c>
+      <c r="X26" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-4800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>200</v>
       </c>
       <c r="S27" s="3">
         <v>1000</v>
       </c>
       <c r="T27" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="U27" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W27" s="3">
+        <v>400</v>
+      </c>
+      <c r="X27" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2394,14 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2285,29 +2424,29 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2318,87 +2457,99 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-4800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R33" s="3">
-        <v>200</v>
       </c>
       <c r="S33" s="3">
         <v>1000</v>
       </c>
       <c r="T33" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="U33" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W33" s="3">
+        <v>400</v>
+      </c>
+      <c r="X33" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2616,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-4800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R35" s="3">
-        <v>200</v>
       </c>
       <c r="S35" s="3">
         <v>1000</v>
       </c>
       <c r="T35" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="U35" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W35" s="3">
+        <v>400</v>
+      </c>
+      <c r="X35" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43008</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42825</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42735</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,64 +2829,66 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F41" s="3">
         <v>18500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>600</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2726,16 +2899,22 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2794,22 +2973,28 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1600</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1300</v>
       </c>
       <c r="H43" s="3">
         <v>1300</v>
@@ -2818,41 +3003,41 @@
         <v>1300</v>
       </c>
       <c r="J43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L43" s="3">
         <v>1600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>9700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>6100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>3300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5900</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,28 +3047,34 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F44" s="3">
         <v>1600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>800</v>
-      </c>
-      <c r="H44" s="3">
-        <v>600</v>
-      </c>
-      <c r="I44" s="3">
-        <v>600</v>
       </c>
       <c r="J44" s="3">
         <v>600</v>
@@ -2892,35 +3083,35 @@
         <v>600</v>
       </c>
       <c r="L44" s="3">
+        <v>600</v>
+      </c>
+      <c r="M44" s="3">
+        <v>600</v>
+      </c>
+      <c r="N44" s="3">
         <v>700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1500</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,65 +3121,71 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,65 +3195,71 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F46" s="3">
         <v>22000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>22000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>14200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>13500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>19500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>19500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>22100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>17500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>15600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>7500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,8 +3269,14 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3098,21 +3307,21 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>3500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3122,11 +3331,11 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3134,8 +3343,14 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3146,53 +3361,53 @@
         <v>400</v>
       </c>
       <c r="F48" s="3">
+        <v>400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>400</v>
+      </c>
+      <c r="H48" s="3">
         <v>600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>1900</v>
       </c>
       <c r="O48" s="3">
         <v>1900</v>
       </c>
       <c r="P48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>600</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,8 +3417,14 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3238,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3">
         <v>100</v>
@@ -3253,13 +3474,13 @@
         <v>100</v>
       </c>
       <c r="S49" s="3">
-        <v>0</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T49" s="3">
+        <v>100</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3270,8 +3491,14 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,61 +3639,67 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>8500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>8300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>8300</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>8700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>8700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>8400</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3474,8 +3713,14 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,65 +3787,71 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F54" s="3">
         <v>31000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>31000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>23100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>23100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>14600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>22200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>24000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>21700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>23000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>8000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>7700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3861,14 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,22 +3921,24 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1300</v>
       </c>
       <c r="H57" s="3">
         <v>1300</v>
@@ -3686,41 +3947,41 @@
         <v>1300</v>
       </c>
       <c r="J57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L57" s="3">
         <v>1400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1600</v>
       </c>
       <c r="M57" s="3">
         <v>1400</v>
       </c>
       <c r="N57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P57" s="3">
         <v>1900</v>
-      </c>
-      <c r="O57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1700</v>
       </c>
       <c r="Q57" s="3">
         <v>2000</v>
       </c>
       <c r="R57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,65 +3991,71 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>9600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>9600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>3400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>8600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>8600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>6700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3798,65 +4065,71 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F59" s="3">
         <v>2700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>4400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,65 +4139,71 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F60" s="3">
         <v>15700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>15700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>8900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>8900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>9200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>12300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,16 +4213,22 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>300</v>
@@ -3958,29 +4243,29 @@
         <v>300</v>
       </c>
       <c r="J61" s="3">
+        <v>300</v>
+      </c>
+      <c r="K61" s="3">
+        <v>300</v>
+      </c>
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4287,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4040,11 +4331,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -4058,20 +4349,26 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,65 +4583,71 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F66" s="3">
         <v>16000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>16000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>6400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4657,14 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4907,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,65 +4981,71 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-25500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-25500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-24700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-24700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-31300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-31300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-21600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-21600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-17200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-5800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-7200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +5055,14 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,65 +5277,71 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F76" s="3">
         <v>15000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>13900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>18500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>11400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5351,14 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5425,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43008</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42825</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42735</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-4800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="R81" s="3">
-        <v>200</v>
       </c>
       <c r="S81" s="3">
         <v>1000</v>
       </c>
       <c r="T81" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="U81" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W81" s="3">
+        <v>400</v>
+      </c>
+      <c r="X81" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5610,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5227,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5248,32 +5645,32 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5283,8 +5680,14 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,16 +6050,22 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="E89" s="3">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="F89" s="3">
         <v>-700</v>
@@ -5641,47 +6074,47 @@
         <v>-700</v>
       </c>
       <c r="H89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5691,8 +6124,14 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,64 +6156,66 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -5785,8 +6226,14 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6374,14 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5954,32 +6413,32 @@
         <v>0</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>2700</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-5500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>500</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5989,8 +6448,14 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6047,11 +6514,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -6083,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,65 +6772,71 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>600</v>
+      </c>
+      <c r="F100" s="3">
         <v>3600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>7000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>7000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-5500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-3900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>6900</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6355,64 +6846,70 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
-      </c>
-      <c r="J101" s="3">
-        <v>100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>100</v>
       </c>
       <c r="L101" s="3">
         <v>100</v>
       </c>
       <c r="M101" s="3">
+        <v>100</v>
+      </c>
+      <c r="N101" s="3">
+        <v>100</v>
+      </c>
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6423,64 +6920,70 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F102" s="3">
         <v>3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-3000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>7200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>500</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6489,6 +6992,12 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SXTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>SXTC</t>
   </si>
@@ -656,137 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43190</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43008</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42825</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>500</v>
       </c>
       <c r="J8" s="3">
         <v>500</v>
@@ -795,52 +803,58 @@
         <v>500</v>
       </c>
       <c r="L8" s="3">
+        <v>500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>500</v>
+      </c>
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>3900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>3200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -857,64 +871,70 @@
         <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>300</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -943,52 +963,58 @@
         <v>100</v>
       </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>2900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>2600</v>
-      </c>
-      <c r="V10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="W10" s="3">
-        <v>700</v>
       </c>
       <c r="X10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1041,10 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1117,14 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1197,14 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1180,39 +1220,39 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>5600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,11 +1265,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1237,8 +1277,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1255,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1276,10 +1322,10 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1311,8 +1357,14 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1388,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>-3100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>-3100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>5100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
-      </c>
-      <c r="S18" s="3">
-        <v>1300</v>
-      </c>
-      <c r="T18" s="3">
-        <v>300</v>
       </c>
       <c r="U18" s="3">
         <v>1300</v>
       </c>
       <c r="V18" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="W18" s="3">
-        <v>600</v>
+        <v>1300</v>
       </c>
       <c r="X18" s="3">
         <v>1100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1578,10 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1542,29 +1610,29 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1575,101 +1643,113 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>3700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>100</v>
@@ -1678,35 +1758,35 @@
         <v>100</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>-100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>-100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1716,11 +1796,11 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -1734,82 +1814,94 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>3300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="T23" s="3">
-        <v>300</v>
       </c>
       <c r="U23" s="3">
         <v>1300</v>
       </c>
       <c r="V23" s="3">
+        <v>300</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1846,44 +1938,50 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>-100</v>
       </c>
       <c r="S24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
       </c>
       <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>300</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-4800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
-      </c>
-      <c r="S26" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T26" s="3">
-        <v>200</v>
       </c>
       <c r="U26" s="3">
         <v>1000</v>
       </c>
       <c r="V26" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="W26" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T27" s="3">
-        <v>200</v>
       </c>
       <c r="U27" s="3">
         <v>1000</v>
       </c>
       <c r="V27" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="W27" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2534,14 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2430,29 +2570,29 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2463,93 +2603,105 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
-      </c>
-      <c r="S33" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T33" s="3">
-        <v>200</v>
       </c>
       <c r="U33" s="3">
         <v>1000</v>
       </c>
       <c r="V33" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="W33" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
-      </c>
-      <c r="S35" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T35" s="3">
-        <v>200</v>
       </c>
       <c r="U35" s="3">
         <v>1000</v>
       </c>
       <c r="V35" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="W35" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43190</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43008</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42825</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,70 +3003,72 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>21200</v>
+      </c>
+      <c r="F41" s="3">
         <v>18100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>11500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>17400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>600</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2905,8 +3079,14 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2917,10 +3097,10 @@
         <v>100</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -2979,28 +3159,34 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1600</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1300</v>
       </c>
       <c r="J43" s="3">
         <v>1300</v>
@@ -3009,41 +3195,41 @@
         <v>1300</v>
       </c>
       <c r="L43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M43" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N43" s="3">
         <v>1600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>8100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>8400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>9700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>6100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>4300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5900</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,34 +3239,40 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>800</v>
-      </c>
-      <c r="J44" s="3">
-        <v>600</v>
-      </c>
-      <c r="K44" s="3">
-        <v>600</v>
       </c>
       <c r="L44" s="3">
         <v>600</v>
@@ -3089,35 +3281,35 @@
         <v>600</v>
       </c>
       <c r="N44" s="3">
+        <v>600</v>
+      </c>
+      <c r="O44" s="3">
+        <v>600</v>
+      </c>
+      <c r="P44" s="3">
         <v>700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>1000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>1300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1500</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,8 +3319,14 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3138,60 +3336,60 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,71 +3399,77 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>26000</v>
+      </c>
+      <c r="F46" s="3">
         <v>21300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>21300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>22000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>22000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>14200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>13500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>19500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>22100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>19600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>15600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>6500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>6100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>7500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,8 +3479,14 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3313,21 +3523,21 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>3500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3337,11 +3547,11 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3349,16 +3559,22 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F48" s="3">
         <v>400</v>
@@ -3367,53 +3583,53 @@
         <v>400</v>
       </c>
       <c r="H48" s="3">
+        <v>400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>400</v>
+      </c>
+      <c r="J48" s="3">
         <v>600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>1900</v>
       </c>
       <c r="Q48" s="3">
         <v>1900</v>
       </c>
       <c r="R48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T48" s="3">
         <v>1800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3423,8 +3639,14 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3465,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="P49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R49" s="3">
         <v>100</v>
@@ -3480,13 +3702,13 @@
         <v>100</v>
       </c>
       <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="V49" s="3">
+        <v>100</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3497,8 +3719,14 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3879,14 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3656,56 +3896,56 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>8500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>8500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>8300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>8300</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>8700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>8400</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3719,8 +3959,14 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,71 +4039,77 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>26400</v>
+      </c>
+      <c r="F54" s="3">
         <v>21700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>21700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>31000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>31000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>23100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>23100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>29600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>29600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>22200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>24000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>21700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>23000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>8000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>7700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>8100</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +4119,14 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,28 +4183,30 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1300</v>
       </c>
       <c r="J57" s="3">
         <v>1300</v>
@@ -3953,41 +4215,41 @@
         <v>1300</v>
       </c>
       <c r="L57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N57" s="3">
         <v>1400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1600</v>
       </c>
       <c r="O57" s="3">
         <v>1400</v>
       </c>
       <c r="P57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R57" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1700</v>
       </c>
       <c r="S57" s="3">
         <v>2000</v>
       </c>
       <c r="T57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2900</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,71 +4259,77 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>9600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>9600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>8600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>8600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1600</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>6700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,8 +4339,14 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4083,59 +4357,59 @@
         <v>2300</v>
       </c>
       <c r="F59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H59" s="3">
         <v>2700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>4400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,8 +4419,14 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4157,59 +4437,59 @@
         <v>6000</v>
       </c>
       <c r="F60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H60" s="3">
         <v>15700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>15700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>10800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>6300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>5100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,8 +4499,14 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4231,10 +4517,10 @@
         <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>300</v>
@@ -4249,29 +4535,29 @@
         <v>300</v>
       </c>
       <c r="L61" s="3">
+        <v>300</v>
+      </c>
+      <c r="M61" s="3">
+        <v>300</v>
+      </c>
+      <c r="N61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>900</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4293,8 +4579,14 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4337,11 +4629,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -4355,20 +4647,26 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,71 +4899,77 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F66" s="3">
         <v>6200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>16000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>16000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>9500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>6400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4979,14 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,71 +5329,77 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-28000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-25500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-25500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-24700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-24700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-31300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-31300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-21600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-21600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-17200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-5800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1400</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5409,14 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,71 +5649,77 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F76" s="3">
         <v>15400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>14700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>14700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>18500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>11400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>11100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5729,14 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="F80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43190</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43008</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42825</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
-      </c>
-      <c r="S81" s="3">
-        <v>1000</v>
-      </c>
-      <c r="T81" s="3">
-        <v>200</v>
       </c>
       <c r="U81" s="3">
         <v>1000</v>
       </c>
       <c r="V81" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="W81" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +6008,10 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5630,10 +6028,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
@@ -5651,32 +6049,32 @@
         <v>100</v>
       </c>
       <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5686,8 +6084,14 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,22 +6484,28 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-700</v>
       </c>
       <c r="H89" s="3">
         <v>-700</v>
@@ -6080,47 +6514,47 @@
         <v>-700</v>
       </c>
       <c r="J89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3">
         <v>1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6130,8 +6564,14 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,70 +6598,72 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6232,8 +6674,14 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,16 +6834,22 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -6419,32 +6879,32 @@
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>2700</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-5500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6454,8 +6914,14 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6948,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6520,11 +6988,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6556,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,71 +7264,77 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>7000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>7000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-5500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>6900</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6852,70 +7344,76 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>100</v>
       </c>
       <c r="N101" s="3">
         <v>100</v>
       </c>
       <c r="O101" s="3">
+        <v>100</v>
+      </c>
+      <c r="P101" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -6926,70 +7424,76 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>7200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>7200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>3100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3">
         <v>500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -6998,6 +7502,12 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
